--- a/forms/trg/Formulir_TRG_sri.xlsx
+++ b/forms/trg/Formulir_TRG_sri.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Ir. Suharman Hamzah, Ph.D (Eng.), HSE</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Hasanuddin University</t>
@@ -955,7 +959,7 @@
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -996,7 +1000,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1037,7 +1041,7 @@
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1070,7 +1074,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1107,7 +1111,7 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
@@ -1144,7 +1148,7 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
@@ -1181,7 +1185,7 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1210,11 +1214,15 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>This research analyzes land use change (LULC) in Makassar City over the last two decades using the Support Vector Machine (SVM) algorithm. These changes have an impact on land surface temperature (LST) and the phenomenon of Surface Urban Heat Islands (SUHI). To assess the impact, the Urban Thermal Field Variance Index (UTFVI) was used. Statistical analysis was conducted with Multivariate Linear Regression (MLR) and Geographically Weighted Regression (GWR) to understand the relationship between LULC, ESG and UTFVI. This study aims to ensure sustainable development and measure urban health in Makassar.</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
